--- a/artfynd/S 610-2026 artfynd.xlsx
+++ b/artfynd/S 610-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024816</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -930,6 +940,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024836</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1059,6 +1074,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1188,6 +1208,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024890</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1317,6 +1342,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024932</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1446,6 +1476,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84024944</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1570,6 +1605,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113774880</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1700,6 +1740,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113774887</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1826,6 +1871,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86110098</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1964,6 +2014,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118342025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2091,6 +2146,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118342116</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2202,6 +2262,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101518071</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2321,6 +2386,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120148521</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2428,6 +2498,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103508037</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2545,6 +2620,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132883030</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2669,6 +2749,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122995072</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2777,6 +2862,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66357691</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2888,6 +2978,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4147750</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3014,6 +3109,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15117111</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3116,6 +3216,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4249394</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3223,6 +3328,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635464</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3330,6 +3440,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635465</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3437,6 +3552,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635466</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3544,6 +3664,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635467</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3672,6 +3797,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78635778</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3786,6 +3916,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118374682</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3900,6 +4035,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118374710</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4014,6 +4154,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118374767</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4137,6 +4282,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118374793</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4253,6 +4403,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67876542</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4376,6 +4531,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134523749</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4478,6 +4638,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4148051</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4610,6 +4775,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115730279</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4735,6 +4905,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130734</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4865,6 +5040,11 @@
       <c r="AY36" t="inlineStr">
         <is>
           <t>Skogsprojektet</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115730289</t>
         </is>
       </c>
     </row>
@@ -4978,8 +5158,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115653355</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 610-2026 artfynd.xlsx
+++ b/artfynd/S 610-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1879,64 +1879,62 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118342025</v>
+        <v>135761292</v>
       </c>
       <c r="B11" t="n">
-        <v>58114</v>
+        <v>58066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>102626</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Ulvsbomursvägen, Ramnäs, Vstm, Ulvsbomursvägen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561010</v>
+        <v>561399</v>
       </c>
       <c r="R11" t="n">
-        <v>6631255</v>
+        <v>6632009</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1960,27 +1958,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flög vidare åt syd.</t>
+          <t>Jagar insekter längs grusvägskanterna</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1994,12 +1992,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gran/tallskog</t>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2010,53 +2003,60 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118342025</t>
+          <t>https://artportalen.se/Sighting/135761292</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118342116</v>
+        <v>118342025</v>
       </c>
       <c r="B12" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2072,7 +2072,7 @@
         <v>6631255</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Talllåga</t>
+          <t>Flög vidare åt syd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2125,13 +2125,17 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gran/tallskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2148,62 +2152,63 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118342116</t>
+          <t>https://artportalen.se/Sighting/118342025</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101518071</v>
+        <v>118342116</v>
       </c>
       <c r="B13" t="n">
-        <v>110078</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Björksnarssjön NO, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558649</v>
+        <v>561010</v>
       </c>
       <c r="R13" t="n">
-        <v>6631408</v>
+        <v>6631255</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2227,12 +2232,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Talllåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2245,35 +2265,35 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gammal körväg i ungtallskog</t>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors, Bengt Eriksson, Sören Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101518071</t>
+          <t>https://artportalen.se/Sighting/118342116</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120148521</v>
+        <v>101518071</v>
       </c>
       <c r="B14" t="n">
-        <v>93235</v>
+        <v>110078</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2281,48 +2301,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långsvadmossen N, Vstm</t>
+          <t>Lilla Björksnarssjön NO, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560926</v>
+        <v>558649</v>
       </c>
       <c r="R14" t="n">
-        <v>6631147</v>
+        <v>6631408</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2346,17 +2363,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2+1</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2371,7 +2383,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Gammal körväg i ungtallskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2388,55 +2400,62 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120148521</t>
+          <t>https://artportalen.se/Sighting/101518071</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103508037</v>
+        <v>120148521</v>
       </c>
       <c r="B15" t="n">
-        <v>97983</v>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långsvadmossen, Vstm</t>
+          <t>Långsvadmossen N, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560961</v>
+        <v>560926</v>
       </c>
       <c r="R15" t="n">
-        <v>6631104</v>
+        <v>6631147</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2463,12 +2482,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2+1</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2483,7 +2507,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Fuktig barrblandskog, lövinslag</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2500,16 +2524,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103508037</t>
+          <t>https://artportalen.se/Sighting/120148521</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132883030</v>
+        <v>103508037</v>
       </c>
       <c r="B16" t="n">
-        <v>8460</v>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2517,42 +2541,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björksnarsjömossen, Ramnäs, Björksnarsjömossen, Ramnäs, Vstm</t>
+          <t>Långsvadmossen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558145</v>
+        <v>560961</v>
       </c>
       <c r="R16" t="n">
-        <v>6631451</v>
+        <v>6631104</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2576,22 +2599,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2600,88 +2613,82 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Fuktig barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132883030</t>
+          <t>https://artportalen.se/Sighting/103508037</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122995072</v>
+        <v>132883030</v>
       </c>
       <c r="B17" t="n">
-        <v>58114</v>
+        <v>8460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Klysen, Ramnäs sn, Vstm</t>
+          <t>Björksnarsjömossen, Ramnäs, Björksnarsjömossen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555477</v>
+        <v>558145</v>
       </c>
       <c r="R17" t="n">
-        <v>6629091</v>
+        <v>6631451</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2705,27 +2712,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Lämplig häckmiljö</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2736,77 +2738,83 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122995072</t>
+          <t>https://artportalen.se/Sighting/132883030</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66357691</v>
+        <v>122995072</v>
       </c>
       <c r="B18" t="n">
-        <v>97989</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>F.d. Klysenbrännan, Ramnäs sn, Vstm</t>
+          <t>Klysen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555323</v>
+        <v>555477</v>
       </c>
       <c r="R18" t="n">
-        <v>6629239</v>
+        <v>6629091</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2833,12 +2841,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Lämplig häckmiljö</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2864,13 +2887,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66357691</t>
+          <t>https://artportalen.se/Sighting/122995072</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4147750</v>
+        <v>66357691</v>
       </c>
       <c r="B19" t="n">
         <v>97989</v>
@@ -2908,16 +2931,18 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Klysenbrändan, Ramnäs sn, Vstm</t>
+          <t>F.d. Klysenbrännan, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555770</v>
+        <v>555323</v>
       </c>
       <c r="R19" t="n">
-        <v>6629036</v>
+        <v>6629239</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2944,12 +2969,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2010-05-31</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2010-05-31</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2960,11 +2985,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Gles tallskog på fin morän</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2974,44 +2994,44 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Sören Larsson, Greta Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4147750</t>
+          <t>https://artportalen.se/Sighting/66357691</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>15117111</v>
+        <v>4147750</v>
       </c>
       <c r="B20" t="n">
-        <v>43378</v>
+        <v>97989</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>201075</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3019,34 +3039,24 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ljusvattsmossen, Ramnäs sn, Vstm</t>
+          <t>Klysenbrändan, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556324</v>
+        <v>555770</v>
       </c>
       <c r="R20" t="n">
-        <v>6627898</v>
+        <v>6629036</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3070,22 +3080,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2012-07-11</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2010-05-31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2012-07-11</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2010-05-31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3096,6 +3096,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Gles tallskog på fin morän</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3111,54 +3116,73 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15117111</t>
+          <t>https://artportalen.se/Sighting/4147750</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4249394</v>
+        <v>15117111</v>
       </c>
       <c r="B21" t="n">
-        <v>97986</v>
+        <v>43378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>201075</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ljusvattsmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556340</v>
+        <v>556324</v>
       </c>
       <c r="R21" t="n">
-        <v>6627920</v>
+        <v>6627898</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3182,12 +3206,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2010-09-07</t>
+          <t>2012-07-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2010-09-07</t>
+          <t>2012-07-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3198,11 +3232,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Ung talskog, skogsbilväg</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3218,33 +3247,33 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4249394</t>
+          <t>https://artportalen.se/Sighting/15117111</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>78635464</v>
+        <v>4249394</v>
       </c>
       <c r="B22" t="n">
-        <v>102464</v>
+        <v>97986</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221343</v>
+        <v>221946</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3253,24 +3282,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Naddtorpetvägen, Vstm</t>
+          <t>Ljusvattsmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564496</v>
+        <v>556340</v>
       </c>
       <c r="R22" t="n">
-        <v>6627141</v>
+        <v>6627920</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3294,12 +3318,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
+          <t>2010-09-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
+          <t>2010-09-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3313,30 +3337,30 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Gammal grusväg i skog</t>
+          <t>Ung talskog, skogsbilväg</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78635464</t>
+          <t>https://artportalen.se/Sighting/4249394</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>78635465</v>
+        <v>78635464</v>
       </c>
       <c r="B23" t="n">
         <v>102464</v>
@@ -3376,10 +3400,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564516</v>
+        <v>564496</v>
       </c>
       <c r="R23" t="n">
-        <v>6626997</v>
+        <v>6627141</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3442,13 +3466,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78635465</t>
+          <t>https://artportalen.se/Sighting/78635464</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>78635466</v>
+        <v>78635465</v>
       </c>
       <c r="B24" t="n">
         <v>102464</v>
@@ -3488,10 +3512,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564513</v>
+        <v>564516</v>
       </c>
       <c r="R24" t="n">
-        <v>6626977</v>
+        <v>6626997</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3554,13 +3578,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78635466</t>
+          <t>https://artportalen.se/Sighting/78635465</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>78635467</v>
+        <v>78635466</v>
       </c>
       <c r="B25" t="n">
         <v>102464</v>
@@ -3600,10 +3624,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564512</v>
+        <v>564513</v>
       </c>
       <c r="R25" t="n">
-        <v>6626953</v>
+        <v>6626977</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3666,13 +3690,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78635467</t>
+          <t>https://artportalen.se/Sighting/78635466</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>78635778</v>
+        <v>78635467</v>
       </c>
       <c r="B26" t="n">
         <v>102464</v>
@@ -3700,36 +3724,25 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Naddtorpetvägen (brunklöver2), Vstm</t>
+          <t>Naddtorpetvägen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564505</v>
+        <v>564512</v>
       </c>
       <c r="R26" t="n">
-        <v>6626956</v>
+        <v>6626953</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3751,11 +3764,6 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>U-Sur-0200</t>
-        </is>
-      </c>
       <c r="Y26" t="inlineStr">
         <is>
           <t>2019-06-27</t>
@@ -3766,20 +3774,19 @@
           <t>2019-06-27</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca 550 blommande plantor. Spridd längs vägen. Koord: 6628306/1519364/5 m; 6628359/1519349/5 m; 6628383/1519337/5 m; 6628402/1519331/5 m; 6628410/1519327/5 m; 6628442/1519315/5 m; 6628465/1519309/5 m; 6628489/1519310/5 m; 6628509/1519314/5 m; 6628653/1519295/5 m;</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Gammal grusväg i skog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3792,20 +3799,16 @@
           <t>Einar Marklund</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78635778</t>
+          <t>https://artportalen.se/Sighting/78635467</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118374682</v>
+        <v>78635778</v>
       </c>
       <c r="B27" t="n">
         <v>102464</v>
@@ -3835,7 +3838,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>550</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3852,17 +3855,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Naddtorpsvägen, Vstm</t>
+          <t>Naddtorpetvägen (brunklöver2), Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564509</v>
+        <v>564505</v>
       </c>
       <c r="R27" t="n">
-        <v>6626951</v>
+        <v>6626956</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3884,14 +3887,24 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>U-Sur-0200</t>
+        </is>
+      </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2019-06-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ca 550 blommande plantor. Spridd längs vägen. Koord: 6628306/1519364/5 m; 6628359/1519349/5 m; 6628383/1519337/5 m; 6628402/1519331/5 m; 6628410/1519327/5 m; 6628442/1519315/5 m; 6628465/1519309/5 m; 6628489/1519310/5 m; 6628509/1519314/5 m; 6628653/1519295/5 m;</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3912,19 +3925,23 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Einar Marklund, Lise-Lotte Norin</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118374682</t>
+          <t>https://artportalen.se/Sighting/78635778</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118374710</v>
+        <v>118374682</v>
       </c>
       <c r="B28" t="n">
         <v>102464</v>
@@ -3954,7 +3971,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3975,10 +3992,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564504</v>
+        <v>564509</v>
       </c>
       <c r="R28" t="n">
-        <v>6626955</v>
+        <v>6626951</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4037,13 +4054,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118374710</t>
+          <t>https://artportalen.se/Sighting/118374682</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118374767</v>
+        <v>118374710</v>
       </c>
       <c r="B29" t="n">
         <v>102464</v>
@@ -4073,7 +4090,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4094,10 +4111,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564500</v>
+        <v>564504</v>
       </c>
       <c r="R29" t="n">
-        <v>6626961</v>
+        <v>6626955</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4156,13 +4173,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118374767</t>
+          <t>https://artportalen.se/Sighting/118374710</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118374793</v>
+        <v>118374767</v>
       </c>
       <c r="B30" t="n">
         <v>102464</v>
@@ -4192,7 +4209,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4209,14 +4226,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Naddtorpetvägen (brunklöver1), Vstm</t>
+          <t>Naddtorpsvägen, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564521</v>
+        <v>564500</v>
       </c>
       <c r="R30" t="n">
-        <v>6627023</v>
+        <v>6626961</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4241,11 +4258,6 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>U-Sur-0815</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>2024-07-11</t>
@@ -4277,23 +4289,19 @@
           <t>Einar Marklund, Lise-Lotte Norin</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118374793</t>
+          <t>https://artportalen.se/Sighting/118374767</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>67876542</v>
+        <v>118374793</v>
       </c>
       <c r="B31" t="n">
-        <v>89104</v>
+        <v>102464</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4301,43 +4309,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>805</v>
+        <v>221343</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Naddtorpet S, Vstm</t>
+          <t>Naddtorpetvägen (brunklöver1), Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564415</v>
+        <v>564521</v>
       </c>
       <c r="R31" t="n">
-        <v>6626815</v>
+        <v>6627023</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4362,14 +4377,19 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>U-Sur-0815</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2017-10-07</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2017-10-07</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4378,94 +4398,82 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kraftledningsgata</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>I gräs</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars Bsenko</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Bsenko</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Einar Marklund, Lise-Lotte Norin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67876542</t>
+          <t>https://artportalen.se/Sighting/118374793</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134523749</v>
+        <v>67876542</v>
       </c>
       <c r="B32" t="n">
-        <v>56606</v>
+        <v>89104</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100130</v>
+        <v>805</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Buskmus</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sicista betulina</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pallas, 1779)</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sothällen SV (linja), Vstm</t>
+          <t>Naddtorpet S, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564313</v>
+        <v>564415</v>
       </c>
       <c r="R32" t="n">
-        <v>6626840</v>
+        <v>6626815</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4492,17 +4500,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2000-07-03</t>
+          <t>2017-10-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2000-07-03</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Klättrade i örnbräken.</t>
+          <t>2017-10-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4516,33 +4519,38 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Telefonlinjegata, örtrikt</t>
+          <t>Kraftledningsgata</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>I gräs</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Lars Bsenko</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Lars Bsenko</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134523749</t>
+          <t>https://artportalen.se/Sighting/67876542</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4148051</v>
+        <v>134523749</v>
       </c>
       <c r="B33" t="n">
-        <v>97989</v>
+        <v>56606</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4550,24 +4558,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>100130</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Buskmus</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sicista betulina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Pallas, 1779)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sothällen SV (linja), Vstm</t>
@@ -4604,12 +4628,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2011-06-08</t>
+          <t>2000-07-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2011-06-08</t>
+          <t>2000-07-03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Klättrade i örnbräken.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4623,7 +4652,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Linjegata, örtrik, enbuskar, lövsly, omgiven av barrblandskog.</t>
+          <t>Telefonlinjegata, örtrikt</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4640,16 +4669,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4148051</t>
+          <t>https://artportalen.se/Sighting/134523749</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115730279</v>
+        <v>4148051</v>
       </c>
       <c r="B34" t="n">
-        <v>57141</v>
+        <v>97989</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4657,50 +4686,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Sothällen SV (linja), Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562109</v>
+        <v>564313</v>
       </c>
       <c r="R34" t="n">
-        <v>6625729</v>
+        <v>6626840</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4727,27 +4740,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2011-06-08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Mycket spillning spridda</t>
+          <t>2011-06-08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4758,35 +4756,36 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Linjegata, örtrik, enbuskar, lövsly, omgiven av barrblandskog.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115730279</t>
+          <t>https://artportalen.se/Sighting/4148051</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130130734</v>
+        <v>115730279</v>
       </c>
       <c r="B35" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4816,11 +4815,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>hane</t>
@@ -4831,21 +4826,17 @@
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562200</v>
+        <v>562109</v>
       </c>
       <c r="R35" t="n">
-        <v>6625910</v>
+        <v>6625729</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4875,9 +4866,24 @@
           <t>2024-04-03</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Mycket spillning spridda</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4892,12 +4898,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4907,67 +4913,75 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130130734</t>
+          <t>https://artportalen.se/Sighting/115730279</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115730289</v>
+        <v>130130734</v>
       </c>
       <c r="B36" t="n">
-        <v>58114</v>
+        <v>57162</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562132</v>
+        <v>562200</v>
       </c>
       <c r="R36" t="n">
-        <v>6625955</v>
+        <v>6625910</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4997,24 +5011,9 @@
           <t>2024-04-03</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-04-03</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Lämplig häckmiljö med en mosse med enstaka lövträd i kanten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5029,12 +5028,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -5044,67 +5043,70 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115730289</t>
+          <t>https://artportalen.se/Sighting/130130734</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115653355</v>
+        <v>115730289</v>
       </c>
       <c r="B37" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562135</v>
+        <v>562132</v>
       </c>
       <c r="R37" t="n">
-        <v>6625832</v>
+        <v>6625955</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5131,34 +5133,168 @@
           <t>2024-04-03</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-04-03</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Lämplig häckmiljö med en mosse med enstaka lövträd i kanten</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115730289</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>115653355</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>562135</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6625832</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/115653355</t>
         </is>
@@ -5202,6 +5338,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 610-2026 artfynd.xlsx
+++ b/artfynd/S 610-2026 artfynd.xlsx
@@ -1882,7 +1882,7 @@
         <v>135761292</v>
       </c>
       <c r="B11" t="n">
-        <v>58066</v>
+        <v>58068</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 610-2026 artfynd.xlsx
+++ b/artfynd/S 610-2026 artfynd.xlsx
@@ -1882,7 +1882,7 @@
         <v>135761292</v>
       </c>
       <c r="B11" t="n">
-        <v>58068</v>
+        <v>58069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 610-2026 artfynd.xlsx
+++ b/artfynd/S 610-2026 artfynd.xlsx
@@ -1882,7 +1882,7 @@
         <v>135761292</v>
       </c>
       <c r="B11" t="n">
-        <v>58069</v>
+        <v>58073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 610-2026 artfynd.xlsx
+++ b/artfynd/S 610-2026 artfynd.xlsx
@@ -1882,7 +1882,7 @@
         <v>135761292</v>
       </c>
       <c r="B11" t="n">
-        <v>58073</v>
+        <v>58074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 610-2026 artfynd.xlsx
+++ b/artfynd/S 610-2026 artfynd.xlsx
@@ -1882,7 +1882,7 @@
         <v>135761292</v>
       </c>
       <c r="B11" t="n">
-        <v>58074</v>
+        <v>58079</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 610-2026 artfynd.xlsx
+++ b/artfynd/S 610-2026 artfynd.xlsx
@@ -1882,7 +1882,7 @@
         <v>135761292</v>
       </c>
       <c r="B11" t="n">
-        <v>58079</v>
+        <v>58092</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
